--- a/final_data_pipeline/output/311224_elec_options.xlsx
+++ b/final_data_pipeline/output/311224_elec_options.xlsx
@@ -1107,7 +1107,7 @@
         <v>173</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -1202,7 +1202,7 @@
         <v>173</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -1297,7 +1297,7 @@
         <v>173</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1392,7 +1392,7 @@
         <v>173</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -1487,7 +1487,7 @@
         <v>173</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE6">
         <v>8000</v>
@@ -1582,7 +1582,7 @@
         <v>173</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE7">
         <v>8000</v>
@@ -1677,7 +1677,7 @@
         <v>173</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE8">
         <v>8000</v>
@@ -1775,7 +1775,7 @@
         <v>173</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1870,7 +1870,7 @@
         <v>173</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1965,7 +1965,7 @@
         <v>173</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -2060,7 +2060,7 @@
         <v>173</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -2155,7 +2155,7 @@
         <v>173</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -2250,7 +2250,7 @@
         <v>173</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE14">
         <v>8000</v>
@@ -2345,7 +2345,7 @@
         <v>173</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE15">
         <v>8000</v>
@@ -2443,7 +2443,7 @@
         <v>173</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE16">
         <v>8000</v>
@@ -2538,7 +2538,7 @@
         <v>173</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE17">
         <v>8000</v>
@@ -2636,7 +2636,7 @@
         <v>173</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE18">
         <v>8000</v>
@@ -2731,7 +2731,7 @@
         <v>173</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE19">
         <v>8000</v>
@@ -2826,7 +2826,7 @@
         <v>173</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE20">
         <v>8000</v>
@@ -2921,7 +2921,7 @@
         <v>173</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE21">
         <v>8000</v>
@@ -4450,7 +4450,7 @@
         <v>173</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE37">
         <v>8000</v>
@@ -4545,7 +4545,7 @@
         <v>173</v>
       </c>
       <c r="AD38">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE38">
         <v>8000</v>
@@ -4640,7 +4640,7 @@
         <v>173</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE39">
         <v>8000</v>
@@ -4738,7 +4738,7 @@
         <v>173</v>
       </c>
       <c r="AD40">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE40">
         <v>8000</v>
@@ -4836,7 +4836,7 @@
         <v>173</v>
       </c>
       <c r="AD41">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE41">
         <v>8000</v>
@@ -4931,7 +4931,7 @@
         <v>173</v>
       </c>
       <c r="AD42">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE42">
         <v>8000</v>
@@ -5026,7 +5026,7 @@
         <v>173</v>
       </c>
       <c r="AD43">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE43">
         <v>8000</v>
@@ -5121,7 +5121,7 @@
         <v>173</v>
       </c>
       <c r="AD44">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE44">
         <v>8000</v>
@@ -5216,7 +5216,7 @@
         <v>173</v>
       </c>
       <c r="AD45">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE45">
         <v>8000</v>
@@ -5311,7 +5311,7 @@
         <v>173</v>
       </c>
       <c r="AD46">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE46">
         <v>8000</v>
@@ -5884,7 +5884,7 @@
         <v>173</v>
       </c>
       <c r="AD52">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE52">
         <v>8000</v>
@@ -5982,7 +5982,7 @@
         <v>173</v>
       </c>
       <c r="AD53">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE53">
         <v>8000</v>
@@ -6077,7 +6077,7 @@
         <v>173</v>
       </c>
       <c r="AD54">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE54">
         <v>8000</v>
@@ -6172,7 +6172,7 @@
         <v>173</v>
       </c>
       <c r="AD55">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE55">
         <v>8000</v>
@@ -6267,7 +6267,7 @@
         <v>173</v>
       </c>
       <c r="AD56">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE56">
         <v>8000</v>
@@ -6362,7 +6362,7 @@
         <v>173</v>
       </c>
       <c r="AD57">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE57">
         <v>8000</v>
@@ -6457,7 +6457,7 @@
         <v>173</v>
       </c>
       <c r="AD58">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE58">
         <v>8000</v>
@@ -6552,7 +6552,7 @@
         <v>173</v>
       </c>
       <c r="AD59">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE59">
         <v>8000</v>
@@ -6647,7 +6647,7 @@
         <v>173</v>
       </c>
       <c r="AD60">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE60">
         <v>8000</v>
@@ -6742,7 +6742,7 @@
         <v>173</v>
       </c>
       <c r="AD61">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE61">
         <v>8000</v>
@@ -6837,7 +6837,7 @@
         <v>173</v>
       </c>
       <c r="AD62">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE62">
         <v>8000</v>
@@ -6932,7 +6932,7 @@
         <v>173</v>
       </c>
       <c r="AD63">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE63">
         <v>8000</v>
@@ -7030,7 +7030,7 @@
         <v>173</v>
       </c>
       <c r="AD64">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE64">
         <v>8000</v>
@@ -7128,7 +7128,7 @@
         <v>173</v>
       </c>
       <c r="AD65">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE65">
         <v>8000</v>
@@ -7223,7 +7223,7 @@
         <v>173</v>
       </c>
       <c r="AD66">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE66">
         <v>8000</v>
@@ -7318,7 +7318,7 @@
         <v>173</v>
       </c>
       <c r="AD67">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE67">
         <v>8000</v>
@@ -7413,7 +7413,7 @@
         <v>173</v>
       </c>
       <c r="AD68">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE68">
         <v>8000</v>
@@ -7508,7 +7508,7 @@
         <v>173</v>
       </c>
       <c r="AD69">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE69">
         <v>8000</v>
@@ -7603,7 +7603,7 @@
         <v>173</v>
       </c>
       <c r="AD70">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE70">
         <v>8000</v>
@@ -7698,7 +7698,7 @@
         <v>173</v>
       </c>
       <c r="AD71">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE71">
         <v>8000</v>
@@ -7793,7 +7793,7 @@
         <v>173</v>
       </c>
       <c r="AD72">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE72">
         <v>8000</v>
@@ -7888,7 +7888,7 @@
         <v>173</v>
       </c>
       <c r="AD73">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE73">
         <v>8000</v>
@@ -7986,7 +7986,7 @@
         <v>173</v>
       </c>
       <c r="AD74">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE74">
         <v>8000</v>
@@ -8084,7 +8084,7 @@
         <v>173</v>
       </c>
       <c r="AD75">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE75">
         <v>8000</v>
@@ -8179,7 +8179,7 @@
         <v>173</v>
       </c>
       <c r="AD76">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE76">
         <v>8000</v>
@@ -8752,7 +8752,7 @@
         <v>173</v>
       </c>
       <c r="AD82">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE82">
         <v>8000</v>
@@ -8847,7 +8847,7 @@
         <v>173</v>
       </c>
       <c r="AD83">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE83">
         <v>8000</v>
@@ -8945,7 +8945,7 @@
         <v>173</v>
       </c>
       <c r="AD84">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE84">
         <v>8000</v>
@@ -9040,7 +9040,7 @@
         <v>173</v>
       </c>
       <c r="AD85">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE85">
         <v>8000</v>
@@ -9135,7 +9135,7 @@
         <v>173</v>
       </c>
       <c r="AD86">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE86">
         <v>8000</v>
@@ -10186,7 +10186,7 @@
         <v>173</v>
       </c>
       <c r="AD97">
-        <v>10</v>
+        <v>16.97685185185183</v>
       </c>
       <c r="AE97">
         <v>8000</v>
@@ -10284,7 +10284,7 @@
         <v>173</v>
       </c>
       <c r="AD98">
-        <v>10</v>
+        <v>16.97685185185183</v>
       </c>
       <c r="AE98">
         <v>8000</v>
@@ -10379,7 +10379,7 @@
         <v>173</v>
       </c>
       <c r="AD99">
-        <v>10</v>
+        <v>16.97685185185183</v>
       </c>
       <c r="AE99">
         <v>8000</v>
@@ -10474,7 +10474,7 @@
         <v>173</v>
       </c>
       <c r="AD100">
-        <v>10</v>
+        <v>16.97685185185183</v>
       </c>
       <c r="AE100">
         <v>8000</v>
@@ -10569,7 +10569,7 @@
         <v>173</v>
       </c>
       <c r="AD101">
-        <v>10</v>
+        <v>16.97685185185183</v>
       </c>
       <c r="AE101">
         <v>8000</v>
@@ -10664,7 +10664,7 @@
         <v>173</v>
       </c>
       <c r="AD102">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE102">
         <v>8000</v>
@@ -10762,7 +10762,7 @@
         <v>173</v>
       </c>
       <c r="AD103">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE103">
         <v>8000</v>
@@ -10857,7 +10857,7 @@
         <v>173</v>
       </c>
       <c r="AD104">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE104">
         <v>8000</v>
@@ -10952,7 +10952,7 @@
         <v>173</v>
       </c>
       <c r="AD105">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE105">
         <v>8000</v>
@@ -11047,7 +11047,7 @@
         <v>173</v>
       </c>
       <c r="AD106">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE106">
         <v>8000</v>
@@ -12098,7 +12098,7 @@
         <v>173</v>
       </c>
       <c r="AD117">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE117">
         <v>8000</v>
@@ -12196,7 +12196,7 @@
         <v>173</v>
       </c>
       <c r="AD118">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE118">
         <v>8000</v>
@@ -12291,7 +12291,7 @@
         <v>173</v>
       </c>
       <c r="AD119">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE119">
         <v>8000</v>
@@ -12386,7 +12386,7 @@
         <v>173</v>
       </c>
       <c r="AD120">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE120">
         <v>8000</v>
@@ -12481,7 +12481,7 @@
         <v>173</v>
       </c>
       <c r="AD121">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE121">
         <v>8000</v>
@@ -12576,7 +12576,7 @@
         <v>173</v>
       </c>
       <c r="AD122">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE122">
         <v>8000</v>
@@ -12671,7 +12671,7 @@
         <v>173</v>
       </c>
       <c r="AD123">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE123">
         <v>8000</v>
@@ -12766,7 +12766,7 @@
         <v>173</v>
       </c>
       <c r="AD124">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE124">
         <v>8000</v>
@@ -12861,7 +12861,7 @@
         <v>173</v>
       </c>
       <c r="AD125">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE125">
         <v>8000</v>
@@ -12959,7 +12959,7 @@
         <v>173</v>
       </c>
       <c r="AD126">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE126">
         <v>8000</v>
@@ -13532,7 +13532,7 @@
         <v>173</v>
       </c>
       <c r="AD132">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AE132">
         <v>8000</v>
@@ -13630,7 +13630,7 @@
         <v>173</v>
       </c>
       <c r="AD133">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AE133">
         <v>8000</v>
@@ -13725,7 +13725,7 @@
         <v>173</v>
       </c>
       <c r="AD134">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AE134">
         <v>8000</v>
@@ -13820,7 +13820,7 @@
         <v>173</v>
       </c>
       <c r="AD135">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AE135">
         <v>8000</v>
@@ -13915,7 +13915,7 @@
         <v>173</v>
       </c>
       <c r="AD136">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AE136">
         <v>8000</v>
@@ -14010,7 +14010,7 @@
         <v>173</v>
       </c>
       <c r="AD137">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE137">
         <v>8000</v>
@@ -14105,7 +14105,7 @@
         <v>173</v>
       </c>
       <c r="AD138">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE138">
         <v>8000</v>
@@ -14200,7 +14200,7 @@
         <v>173</v>
       </c>
       <c r="AD139">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE139">
         <v>8000</v>
@@ -14298,7 +14298,7 @@
         <v>173</v>
       </c>
       <c r="AD140">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE140">
         <v>8000</v>
@@ -14393,7 +14393,7 @@
         <v>173</v>
       </c>
       <c r="AD141">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE141">
         <v>8000</v>
@@ -14488,7 +14488,7 @@
         <v>173</v>
       </c>
       <c r="AD142">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE142">
         <v>8000</v>
@@ -14586,7 +14586,7 @@
         <v>173</v>
       </c>
       <c r="AD143">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE143">
         <v>8000</v>
@@ -14681,7 +14681,7 @@
         <v>173</v>
       </c>
       <c r="AD144">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE144">
         <v>8000</v>
@@ -14776,7 +14776,7 @@
         <v>173</v>
       </c>
       <c r="AD145">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE145">
         <v>8000</v>
@@ -14871,7 +14871,7 @@
         <v>173</v>
       </c>
       <c r="AD146">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE146">
         <v>8000</v>
@@ -14966,7 +14966,7 @@
         <v>173</v>
       </c>
       <c r="AD147">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE147">
         <v>8000</v>
@@ -15064,7 +15064,7 @@
         <v>173</v>
       </c>
       <c r="AD148">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE148">
         <v>8000</v>
@@ -15159,7 +15159,7 @@
         <v>173</v>
       </c>
       <c r="AD149">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE149">
         <v>8000</v>
@@ -15254,7 +15254,7 @@
         <v>173</v>
       </c>
       <c r="AD150">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE150">
         <v>8000</v>
@@ -15349,7 +15349,7 @@
         <v>173</v>
       </c>
       <c r="AD151">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE151">
         <v>8000</v>
@@ -18312,7 +18312,7 @@
         <v>173</v>
       </c>
       <c r="AD182">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE182">
         <v>8000</v>
@@ -18407,7 +18407,7 @@
         <v>173</v>
       </c>
       <c r="AD183">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE183">
         <v>8000</v>
@@ -18502,7 +18502,7 @@
         <v>173</v>
       </c>
       <c r="AD184">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE184">
         <v>8000</v>
@@ -18597,7 +18597,7 @@
         <v>173</v>
       </c>
       <c r="AD185">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE185">
         <v>8000</v>
@@ -18692,7 +18692,7 @@
         <v>173</v>
       </c>
       <c r="AD186">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE186">
         <v>8000</v>
@@ -18790,7 +18790,7 @@
         <v>173</v>
       </c>
       <c r="AD187">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE187">
         <v>8000</v>
@@ -18888,7 +18888,7 @@
         <v>173</v>
       </c>
       <c r="AD188">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE188">
         <v>8000</v>
@@ -18983,7 +18983,7 @@
         <v>173</v>
       </c>
       <c r="AD189">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE189">
         <v>8000</v>
@@ -19078,7 +19078,7 @@
         <v>173</v>
       </c>
       <c r="AD190">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE190">
         <v>8000</v>
@@ -19173,7 +19173,7 @@
         <v>173</v>
       </c>
       <c r="AD191">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE191">
         <v>8000</v>
@@ -19268,7 +19268,7 @@
         <v>173</v>
       </c>
       <c r="AD192">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE192">
         <v>8000</v>
@@ -19363,7 +19363,7 @@
         <v>173</v>
       </c>
       <c r="AD193">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE193">
         <v>8000</v>
@@ -19458,7 +19458,7 @@
         <v>173</v>
       </c>
       <c r="AD194">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE194">
         <v>8000</v>
@@ -19556,7 +19556,7 @@
         <v>173</v>
       </c>
       <c r="AD195">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE195">
         <v>8000</v>
@@ -19654,7 +19654,7 @@
         <v>173</v>
       </c>
       <c r="AD196">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE196">
         <v>8000</v>
@@ -19749,7 +19749,7 @@
         <v>173</v>
       </c>
       <c r="AD197">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE197">
         <v>8000</v>
@@ -19844,7 +19844,7 @@
         <v>173</v>
       </c>
       <c r="AD198">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE198">
         <v>8000</v>
@@ -19939,7 +19939,7 @@
         <v>173</v>
       </c>
       <c r="AD199">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE199">
         <v>8000</v>
@@ -20034,7 +20034,7 @@
         <v>173</v>
       </c>
       <c r="AD200">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE200">
         <v>8000</v>
@@ -20129,7 +20129,7 @@
         <v>173</v>
       </c>
       <c r="AD201">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE201">
         <v>8000</v>
@@ -20705,7 +20705,7 @@
         <v>173</v>
       </c>
       <c r="AD207">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE207">
         <v>8000</v>
@@ -20800,7 +20800,7 @@
         <v>173</v>
       </c>
       <c r="AD208">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE208">
         <v>8000</v>
@@ -20898,7 +20898,7 @@
         <v>173</v>
       </c>
       <c r="AD209">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE209">
         <v>8000</v>
@@ -20993,7 +20993,7 @@
         <v>173</v>
       </c>
       <c r="AD210">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE210">
         <v>8000</v>
@@ -21094,7 +21094,7 @@
         <v>173</v>
       </c>
       <c r="AD211">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE211">
         <v>8000</v>
@@ -21189,7 +21189,7 @@
         <v>173</v>
       </c>
       <c r="AD212">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE212">
         <v>8000</v>
@@ -21284,7 +21284,7 @@
         <v>173</v>
       </c>
       <c r="AD213">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE213">
         <v>8000</v>
@@ -21379,7 +21379,7 @@
         <v>173</v>
       </c>
       <c r="AD214">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE214">
         <v>8000</v>
@@ -21474,7 +21474,7 @@
         <v>173</v>
       </c>
       <c r="AD215">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE215">
         <v>8000</v>
@@ -21569,7 +21569,7 @@
         <v>173</v>
       </c>
       <c r="AD216">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE216">
         <v>8000</v>
@@ -21664,7 +21664,7 @@
         <v>173</v>
       </c>
       <c r="AD217">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE217">
         <v>8000</v>
@@ -21759,7 +21759,7 @@
         <v>173</v>
       </c>
       <c r="AD218">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE218">
         <v>8000</v>
@@ -21854,7 +21854,7 @@
         <v>173</v>
       </c>
       <c r="AD219">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE219">
         <v>8000</v>
@@ -21949,7 +21949,7 @@
         <v>173</v>
       </c>
       <c r="AD220">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE220">
         <v>8000</v>
@@ -22047,7 +22047,7 @@
         <v>173</v>
       </c>
       <c r="AD221">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE221">
         <v>8000</v>
@@ -22142,7 +22142,7 @@
         <v>173</v>
       </c>
       <c r="AD222">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE222">
         <v>8000</v>
@@ -22237,7 +22237,7 @@
         <v>173</v>
       </c>
       <c r="AD223">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE223">
         <v>8000</v>
@@ -22332,7 +22332,7 @@
         <v>173</v>
       </c>
       <c r="AD224">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE224">
         <v>8000</v>
@@ -22430,7 +22430,7 @@
         <v>173</v>
       </c>
       <c r="AD225">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE225">
         <v>8000</v>
@@ -22525,7 +22525,7 @@
         <v>173</v>
       </c>
       <c r="AD226">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE226">
         <v>8000</v>
@@ -22620,7 +22620,7 @@
         <v>173</v>
       </c>
       <c r="AD227">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE227">
         <v>8000</v>
@@ -22721,7 +22721,7 @@
         <v>173</v>
       </c>
       <c r="AD228">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE228">
         <v>8000</v>
@@ -22819,7 +22819,7 @@
         <v>173</v>
       </c>
       <c r="AD229">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE229">
         <v>8000</v>
@@ -22917,7 +22917,7 @@
         <v>173</v>
       </c>
       <c r="AD230">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE230">
         <v>8000</v>
@@ -23012,7 +23012,7 @@
         <v>173</v>
       </c>
       <c r="AD231">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE231">
         <v>8000</v>
@@ -23107,7 +23107,7 @@
         <v>173</v>
       </c>
       <c r="AD232">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE232">
         <v>8000</v>
@@ -23202,7 +23202,7 @@
         <v>173</v>
       </c>
       <c r="AD233">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE233">
         <v>8000</v>
@@ -23297,7 +23297,7 @@
         <v>173</v>
       </c>
       <c r="AD234">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE234">
         <v>8000</v>
@@ -23392,7 +23392,7 @@
         <v>173</v>
       </c>
       <c r="AD235">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE235">
         <v>8000</v>
@@ -23487,7 +23487,7 @@
         <v>173</v>
       </c>
       <c r="AD236">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE236">
         <v>8000</v>
@@ -23582,7 +23582,7 @@
         <v>173</v>
       </c>
       <c r="AD237">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE237">
         <v>8000</v>
@@ -23677,7 +23677,7 @@
         <v>173</v>
       </c>
       <c r="AD238">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE238">
         <v>8000</v>
@@ -23772,7 +23772,7 @@
         <v>173</v>
       </c>
       <c r="AD239">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE239">
         <v>8000</v>
@@ -23867,7 +23867,7 @@
         <v>173</v>
       </c>
       <c r="AD240">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE240">
         <v>8000</v>
@@ -23962,7 +23962,7 @@
         <v>173</v>
       </c>
       <c r="AD241">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE241">
         <v>8000</v>
@@ -24057,7 +24057,7 @@
         <v>173</v>
       </c>
       <c r="AD242">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE242">
         <v>8000</v>
@@ -24152,7 +24152,7 @@
         <v>173</v>
       </c>
       <c r="AD243">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE243">
         <v>8000</v>
@@ -24247,7 +24247,7 @@
         <v>173</v>
       </c>
       <c r="AD244">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE244">
         <v>8000</v>
@@ -24342,7 +24342,7 @@
         <v>173</v>
       </c>
       <c r="AD245">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE245">
         <v>8000</v>
@@ -24437,7 +24437,7 @@
         <v>173</v>
       </c>
       <c r="AD246">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE246">
         <v>8000</v>
@@ -24532,7 +24532,7 @@
         <v>173</v>
       </c>
       <c r="AD247">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE247">
         <v>8000</v>
@@ -24627,7 +24627,7 @@
         <v>173</v>
       </c>
       <c r="AD248">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE248">
         <v>8000</v>
@@ -24722,7 +24722,7 @@
         <v>173</v>
       </c>
       <c r="AD249">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE249">
         <v>8000</v>
@@ -24817,7 +24817,7 @@
         <v>173</v>
       </c>
       <c r="AD250">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE250">
         <v>8000</v>
@@ -24912,7 +24912,7 @@
         <v>173</v>
       </c>
       <c r="AD251">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE251">
         <v>8000</v>
@@ -25007,7 +25007,7 @@
         <v>173</v>
       </c>
       <c r="AD252">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE252">
         <v>8000</v>
@@ -25105,7 +25105,7 @@
         <v>173</v>
       </c>
       <c r="AD253">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE253">
         <v>8000</v>
@@ -25203,7 +25203,7 @@
         <v>173</v>
       </c>
       <c r="AD254">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE254">
         <v>8000</v>
@@ -25298,7 +25298,7 @@
         <v>173</v>
       </c>
       <c r="AD255">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE255">
         <v>8000</v>
@@ -25396,7 +25396,7 @@
         <v>173</v>
       </c>
       <c r="AD256">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE256">
         <v>8000</v>
@@ -25491,7 +25491,7 @@
         <v>173</v>
       </c>
       <c r="AD257">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE257">
         <v>8000</v>
@@ -25589,7 +25589,7 @@
         <v>173</v>
       </c>
       <c r="AD258">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE258">
         <v>8000</v>
@@ -26640,7 +26640,7 @@
         <v>173</v>
       </c>
       <c r="AD269">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE269">
         <v>8000</v>
@@ -26735,7 +26735,7 @@
         <v>173</v>
       </c>
       <c r="AD270">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE270">
         <v>8000</v>
@@ -26830,7 +26830,7 @@
         <v>173</v>
       </c>
       <c r="AD271">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE271">
         <v>8000</v>
@@ -26925,7 +26925,7 @@
         <v>173</v>
       </c>
       <c r="AD272">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE272">
         <v>8000</v>
@@ -27023,7 +27023,7 @@
         <v>173</v>
       </c>
       <c r="AD273">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE273">
         <v>8000</v>
@@ -27121,7 +27121,7 @@
         <v>173</v>
       </c>
       <c r="AD274">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE274">
         <v>8000</v>
@@ -27216,7 +27216,7 @@
         <v>173</v>
       </c>
       <c r="AD275">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE275">
         <v>8000</v>
@@ -27311,7 +27311,7 @@
         <v>173</v>
       </c>
       <c r="AD276">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE276">
         <v>8000</v>
@@ -27406,7 +27406,7 @@
         <v>173</v>
       </c>
       <c r="AD277">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE277">
         <v>8000</v>
@@ -27501,7 +27501,7 @@
         <v>173</v>
       </c>
       <c r="AD278">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE278">
         <v>8000</v>
@@ -27596,7 +27596,7 @@
         <v>173</v>
       </c>
       <c r="AD279">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE279">
         <v>8000</v>
@@ -27691,7 +27691,7 @@
         <v>173</v>
       </c>
       <c r="AD280">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE280">
         <v>8000</v>
@@ -27786,7 +27786,7 @@
         <v>173</v>
       </c>
       <c r="AD281">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE281">
         <v>8000</v>
@@ -27881,7 +27881,7 @@
         <v>173</v>
       </c>
       <c r="AD282">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE282">
         <v>8000</v>
@@ -27979,7 +27979,7 @@
         <v>173</v>
       </c>
       <c r="AD283">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE283">
         <v>8000</v>
@@ -28074,7 +28074,7 @@
         <v>173</v>
       </c>
       <c r="AD284">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE284">
         <v>8000</v>
@@ -28172,7 +28172,7 @@
         <v>173</v>
       </c>
       <c r="AD285">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE285">
         <v>8000</v>
@@ -28267,7 +28267,7 @@
         <v>173</v>
       </c>
       <c r="AD286">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE286">
         <v>8000</v>
@@ -28362,7 +28362,7 @@
         <v>173</v>
       </c>
       <c r="AD287">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE287">
         <v>8000</v>
@@ -28457,7 +28457,7 @@
         <v>173</v>
       </c>
       <c r="AD288">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE288">
         <v>8000</v>
@@ -28552,7 +28552,7 @@
         <v>173</v>
       </c>
       <c r="AD289">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE289">
         <v>8000</v>
@@ -28647,7 +28647,7 @@
         <v>173</v>
       </c>
       <c r="AD290">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE290">
         <v>8000</v>
@@ -28742,7 +28742,7 @@
         <v>173</v>
       </c>
       <c r="AD291">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE291">
         <v>8000</v>
@@ -28837,7 +28837,7 @@
         <v>173</v>
       </c>
       <c r="AD292">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE292">
         <v>8000</v>
@@ -28932,7 +28932,7 @@
         <v>173</v>
       </c>
       <c r="AD293">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE293">
         <v>8000</v>
@@ -29027,7 +29027,7 @@
         <v>173</v>
       </c>
       <c r="AD294">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE294">
         <v>8000</v>
@@ -29125,7 +29125,7 @@
         <v>173</v>
       </c>
       <c r="AD295">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE295">
         <v>8000</v>
@@ -29223,7 +29223,7 @@
         <v>173</v>
       </c>
       <c r="AD296">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE296">
         <v>8000</v>
@@ -29321,7 +29321,7 @@
         <v>173</v>
       </c>
       <c r="AD297">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE297">
         <v>8000</v>
@@ -29419,7 +29419,7 @@
         <v>173</v>
       </c>
       <c r="AD298">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE298">
         <v>8000</v>
@@ -29514,7 +29514,7 @@
         <v>173</v>
       </c>
       <c r="AD299">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE299">
         <v>8000</v>
@@ -29615,7 +29615,7 @@
         <v>173</v>
       </c>
       <c r="AD300">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE300">
         <v>8000</v>
@@ -29710,7 +29710,7 @@
         <v>173</v>
       </c>
       <c r="AD301">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE301">
         <v>8000</v>
@@ -29805,7 +29805,7 @@
         <v>173</v>
       </c>
       <c r="AD302">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE302">
         <v>8000</v>
@@ -29900,7 +29900,7 @@
         <v>173</v>
       </c>
       <c r="AD303">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE303">
         <v>8000</v>
@@ -29998,7 +29998,7 @@
         <v>173</v>
       </c>
       <c r="AD304">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE304">
         <v>8000</v>
@@ -30093,7 +30093,7 @@
         <v>173</v>
       </c>
       <c r="AD305">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE305">
         <v>8000</v>
@@ -30188,7 +30188,7 @@
         <v>173</v>
       </c>
       <c r="AD306">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE306">
         <v>8000</v>
@@ -30283,7 +30283,7 @@
         <v>173</v>
       </c>
       <c r="AD307">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE307">
         <v>8000</v>
@@ -30378,7 +30378,7 @@
         <v>173</v>
       </c>
       <c r="AD308">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE308">
         <v>8000</v>
@@ -30473,7 +30473,7 @@
         <v>173</v>
       </c>
       <c r="AD309">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE309">
         <v>8000</v>
@@ -30568,7 +30568,7 @@
         <v>173</v>
       </c>
       <c r="AD310">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE310">
         <v>8000</v>
@@ -30663,7 +30663,7 @@
         <v>173</v>
       </c>
       <c r="AD311">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE311">
         <v>8000</v>
@@ -30758,7 +30758,7 @@
         <v>173</v>
       </c>
       <c r="AD312">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE312">
         <v>8000</v>
@@ -30853,7 +30853,7 @@
         <v>173</v>
       </c>
       <c r="AD313">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE313">
         <v>8000</v>
@@ -30948,7 +30948,7 @@
         <v>173</v>
       </c>
       <c r="AD314">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE314">
         <v>8000</v>
@@ -31521,7 +31521,7 @@
         <v>173</v>
       </c>
       <c r="AD320">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE320">
         <v>8000</v>
@@ -31616,7 +31616,7 @@
         <v>173</v>
       </c>
       <c r="AD321">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE321">
         <v>8000</v>
@@ -31711,7 +31711,7 @@
         <v>173</v>
       </c>
       <c r="AD322">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE322">
         <v>8000</v>
@@ -31806,7 +31806,7 @@
         <v>173</v>
       </c>
       <c r="AD323">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE323">
         <v>8000</v>
@@ -31904,7 +31904,7 @@
         <v>173</v>
       </c>
       <c r="AD324">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE324">
         <v>8000</v>
@@ -32955,7 +32955,7 @@
         <v>173</v>
       </c>
       <c r="AD335">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE335">
         <v>8000</v>
@@ -33050,7 +33050,7 @@
         <v>173</v>
       </c>
       <c r="AD336">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE336">
         <v>8000</v>
@@ -33145,7 +33145,7 @@
         <v>173</v>
       </c>
       <c r="AD337">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE337">
         <v>8000</v>
@@ -33240,7 +33240,7 @@
         <v>173</v>
       </c>
       <c r="AD338">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE338">
         <v>8000</v>
@@ -33335,7 +33335,7 @@
         <v>173</v>
       </c>
       <c r="AD339">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE339">
         <v>8000</v>
@@ -33430,7 +33430,7 @@
         <v>173</v>
       </c>
       <c r="AD340">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE340">
         <v>8000</v>
@@ -33525,7 +33525,7 @@
         <v>173</v>
       </c>
       <c r="AD341">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE341">
         <v>8000</v>
@@ -33620,7 +33620,7 @@
         <v>173</v>
       </c>
       <c r="AD342">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE342">
         <v>8000</v>
@@ -33715,7 +33715,7 @@
         <v>173</v>
       </c>
       <c r="AD343">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE343">
         <v>8000</v>
@@ -33810,7 +33810,7 @@
         <v>173</v>
       </c>
       <c r="AD344">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE344">
         <v>8000</v>
@@ -33908,7 +33908,7 @@
         <v>173</v>
       </c>
       <c r="AD345">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE345">
         <v>8000</v>
@@ -34003,7 +34003,7 @@
         <v>173</v>
       </c>
       <c r="AD346">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE346">
         <v>8000</v>
@@ -34098,7 +34098,7 @@
         <v>173</v>
       </c>
       <c r="AD347">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE347">
         <v>8000</v>
@@ -34193,7 +34193,7 @@
         <v>173</v>
       </c>
       <c r="AD348">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE348">
         <v>8000</v>
@@ -34291,7 +34291,7 @@
         <v>173</v>
       </c>
       <c r="AD349">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE349">
         <v>8000</v>
@@ -34389,7 +34389,7 @@
         <v>173</v>
       </c>
       <c r="AD350">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE350">
         <v>8000</v>
@@ -34487,7 +34487,7 @@
         <v>173</v>
       </c>
       <c r="AD351">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE351">
         <v>8000</v>
@@ -34582,7 +34582,7 @@
         <v>173</v>
       </c>
       <c r="AD352">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE352">
         <v>8000</v>
@@ -34680,7 +34680,7 @@
         <v>173</v>
       </c>
       <c r="AD353">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE353">
         <v>8000</v>
@@ -34775,7 +34775,7 @@
         <v>173</v>
       </c>
       <c r="AD354">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE354">
         <v>8000</v>
@@ -34870,7 +34870,7 @@
         <v>173</v>
       </c>
       <c r="AD355">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE355">
         <v>8000</v>
@@ -34965,7 +34965,7 @@
         <v>173</v>
       </c>
       <c r="AD356">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE356">
         <v>8000</v>
@@ -35060,7 +35060,7 @@
         <v>173</v>
       </c>
       <c r="AD357">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE357">
         <v>8000</v>
@@ -35155,7 +35155,7 @@
         <v>173</v>
       </c>
       <c r="AD358">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE358">
         <v>8000</v>
@@ -35250,7 +35250,7 @@
         <v>173</v>
       </c>
       <c r="AD359">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE359">
         <v>8000</v>
@@ -36779,7 +36779,7 @@
         <v>173</v>
       </c>
       <c r="AD375">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE375">
         <v>8000</v>
@@ -36877,7 +36877,7 @@
         <v>173</v>
       </c>
       <c r="AD376">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE376">
         <v>8000</v>
@@ -36972,7 +36972,7 @@
         <v>173</v>
       </c>
       <c r="AD377">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE377">
         <v>8000</v>
@@ -37067,7 +37067,7 @@
         <v>173</v>
       </c>
       <c r="AD378">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE378">
         <v>8000</v>
@@ -37162,7 +37162,7 @@
         <v>173</v>
       </c>
       <c r="AD379">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE379">
         <v>8000</v>
@@ -37257,7 +37257,7 @@
         <v>173</v>
       </c>
       <c r="AD380">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE380">
         <v>8000</v>
@@ -37355,7 +37355,7 @@
         <v>173</v>
       </c>
       <c r="AD381">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE381">
         <v>8000</v>
@@ -37450,7 +37450,7 @@
         <v>173</v>
       </c>
       <c r="AD382">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE382">
         <v>8000</v>
@@ -37545,7 +37545,7 @@
         <v>173</v>
       </c>
       <c r="AD383">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE383">
         <v>8000</v>
@@ -37640,7 +37640,7 @@
         <v>173</v>
       </c>
       <c r="AD384">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE384">
         <v>8000</v>
@@ -37735,7 +37735,7 @@
         <v>173</v>
       </c>
       <c r="AD385">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE385">
         <v>8000</v>
@@ -37830,7 +37830,7 @@
         <v>173</v>
       </c>
       <c r="AD386">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE386">
         <v>8000</v>
@@ -37925,7 +37925,7 @@
         <v>173</v>
       </c>
       <c r="AD387">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE387">
         <v>8000</v>
@@ -38020,7 +38020,7 @@
         <v>173</v>
       </c>
       <c r="AD388">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE388">
         <v>8000</v>
@@ -38115,7 +38115,7 @@
         <v>173</v>
       </c>
       <c r="AD389">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE389">
         <v>8000</v>
@@ -38210,7 +38210,7 @@
         <v>173</v>
       </c>
       <c r="AD390">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE390">
         <v>8000</v>
@@ -38308,7 +38308,7 @@
         <v>173</v>
       </c>
       <c r="AD391">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE391">
         <v>8000</v>
@@ -38406,7 +38406,7 @@
         <v>173</v>
       </c>
       <c r="AD392">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE392">
         <v>8000</v>
@@ -38501,7 +38501,7 @@
         <v>173</v>
       </c>
       <c r="AD393">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE393">
         <v>8000</v>
@@ -38596,7 +38596,7 @@
         <v>173</v>
       </c>
       <c r="AD394">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AE394">
         <v>8000</v>
@@ -42037,7 +42037,7 @@
         <v>173</v>
       </c>
       <c r="AD430">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE430">
         <v>8000</v>
@@ -42132,7 +42132,7 @@
         <v>173</v>
       </c>
       <c r="AD431">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE431">
         <v>8000</v>
@@ -42227,7 +42227,7 @@
         <v>173</v>
       </c>
       <c r="AD432">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE432">
         <v>8000</v>
@@ -42322,7 +42322,7 @@
         <v>173</v>
       </c>
       <c r="AD433">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE433">
         <v>8000</v>
@@ -42417,7 +42417,7 @@
         <v>173</v>
       </c>
       <c r="AD434">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE434">
         <v>8000</v>
@@ -42512,7 +42512,7 @@
         <v>173</v>
       </c>
       <c r="AD435">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE435">
         <v>8000</v>
@@ -42610,7 +42610,7 @@
         <v>173</v>
       </c>
       <c r="AD436">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE436">
         <v>8000</v>
@@ -42708,7 +42708,7 @@
         <v>173</v>
       </c>
       <c r="AD437">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE437">
         <v>8000</v>
@@ -42803,7 +42803,7 @@
         <v>173</v>
       </c>
       <c r="AD438">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE438">
         <v>8000</v>
@@ -42898,7 +42898,7 @@
         <v>173</v>
       </c>
       <c r="AD439">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE439">
         <v>8000</v>
